--- a/Result/profitability/6130.xlsx
+++ b/Result/profitability/6130.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.61</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.41875</v>
+        <v>-0.38</v>
       </c>
       <c r="N2" t="n">
-        <v>34.34125</v>
+        <v>35.505</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.54</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.48</v>
+        <v>-0.365</v>
       </c>
       <c r="N3" t="n">
-        <v>33.79875</v>
+        <v>31.76</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.78</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.495</v>
+        <v>-0.415</v>
       </c>
       <c r="N4" t="n">
-        <v>23.705</v>
+        <v>24.9075</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>-1.89</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.68375</v>
+        <v>-0.6074999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>22.19125</v>
+        <v>24.06125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>-0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6549999999999999</v>
+        <v>-0.5812499999999999</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5800000000000001</v>
+        <v>-0.465</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1375,7 +1375,7 @@
         <v>-0.13</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.51375</v>
+        <v>-0.4425</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -9766,6 +9766,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6130</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>50</v>
+      </c>
+      <c r="D75" t="n">
+        <v>29</v>
+      </c>
+      <c r="E75" t="n">
+        <v>21</v>
+      </c>
+      <c r="F75" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.52%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.97125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.838709677419355</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7.259999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2083213773314203</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.742857142857143</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.551012891344383</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
